--- a/artfynd/A 5415-2024 artfynd.xlsx
+++ b/artfynd/A 5415-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5415-2024 artfynd.xlsx
+++ b/artfynd/A 5415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103355466</v>
+        <v>114618678</v>
       </c>
       <c r="B2" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,23 +708,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falun, Dlr</t>
+          <t>Lomstäpporna, Lomstäpporna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548233.6383177886</v>
+        <v>548352</v>
       </c>
       <c r="R2" t="n">
-        <v>6727370.825334971</v>
+        <v>6727344</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +769,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lågörttallskog</t>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Levande vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,12 +810,7 @@
         <v>113750432</v>
       </c>
       <c r="B3" t="n">
-        <v>89736</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +839,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Dlr</t>
+          <t>Hästhagen, Hästhagen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -941,60 +940,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114618678</v>
+        <v>109968003</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomstäpporna (Lomstäpporna), Dlr</t>
+          <t>Lomstäpporna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548352</v>
+        <v>548408</v>
       </c>
       <c r="R4" t="n">
-        <v>6727344</v>
+        <v>6727286</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,12 +1011,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,31 +1027,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Levande vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1078,15 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114618679</v>
+        <v>109970607</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,35 +1054,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Dlr</t>
+          <t>Hästhagen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548299</v>
+        <v>548263</v>
       </c>
       <c r="R5" t="n">
-        <v>6727377</v>
+        <v>6727367</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1149,12 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,12 +1159,7 @@
         <v>114618687</v>
       </c>
       <c r="B6" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1193,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästhagen (Hästhagen), Dlr</t>
+          <t>Hästhagen, Hästhagen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1311,6 +1281,340 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103355466</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548234</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6727371</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörttallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108834594</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lomstäpporna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548419</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6727270</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundborn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114618679</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästhagen, Hästhagen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548299</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6727377</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5415-2024 artfynd.xlsx
+++ b/artfynd/A 5415-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114618678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109968003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108834594</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113750432</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109970607</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,6 +1424,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114618687</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103355466</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,8 +1655,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114618679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>